--- a/optimized_version/metadata/testing_daily_metrics/agus2_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus2_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1501027599326671</v>
+        <v>0.1438611423243448</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1569587034925917</v>
+        <v>0.1504320000000092</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1569587034925917</v>
+        <v>0.1504320000000092</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>0.827324237397179</v>
+        <v>0.8283880638551849</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8354443827512364</v>
+        <v>0.8365321666666669</v>
       </c>
       <c r="F3" t="n">
-        <v>2.507893945169883</v>
+        <v>2.507848446266372</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.093529445729664</v>
+        <v>-1.093453483641733</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1163490442406551</v>
+        <v>0.1147987852888798</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1221480092064772</v>
+        <v>0.1205163333333316</v>
       </c>
       <c r="F4" t="n">
-        <v>0.154290464966348</v>
+        <v>0.1529459640657406</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4519421915684142</v>
+        <v>0.4614522240498247</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4777596108640291</v>
+        <v>0.4786541221262823</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.491178441375616</v>
+        <v>0.492111333333332</v>
       </c>
       <c r="F5" t="n">
-        <v>1.37986546822411</v>
+        <v>1.379991498376223</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2021603759897508</v>
+        <v>-0.2023799848973713</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>1.905308915793579</v>
+        <v>1.90588399274447</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2.059328441375622</v>
+        <v>2.059872333333337</v>
       </c>
       <c r="F6" t="n">
-        <v>4.489894709344785</v>
+        <v>4.489890803377891</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2692409958536511</v>
+        <v>0.2692422672951527</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6506002069463817</v>
+        <v>0.6495808003551152</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7419514505820969</v>
+        <v>0.7408636666666665</v>
       </c>
       <c r="F7" t="n">
-        <v>1.708513086545301</v>
+        <v>1.706120742481023</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9327869933451342</v>
+        <v>0.9329750914768929</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5102418359778712</v>
+        <v>0.5089452687666783</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5659855092064845</v>
+        <v>0.5645261666666718</v>
       </c>
       <c r="F8" t="n">
-        <v>1.947292888192551</v>
+        <v>1.948486029752501</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7516082588701958</v>
+        <v>0.7513037773966104</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>3.965266900115953</v>
+        <v>3.968025074098868</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.428213765502473</v>
+        <v>2.430389333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>9.00329619217694</v>
+        <v>9.004969744024166</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8642664225343766</v>
+        <v>0.8642159569522877</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>3.118892891326893</v>
+        <v>3.117804247643056</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.895118117248763</v>
+        <v>1.894524999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>4.584678384407386</v>
+        <v>4.584922494665602</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5387559773080208</v>
+        <v>0.5387068583140273</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>3.685293219153355</v>
+        <v>3.681275845175721</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.102973734497528</v>
+        <v>3.100798166666667</v>
       </c>
       <c r="F11" t="n">
-        <v>6.909388060214181</v>
+        <v>6.906712758479294</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9446051264651677</v>
+        <v>0.9446480157366893</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3071732074706867</v>
+        <v>0.3071887549395159</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -737,10 +737,10 @@
         <v>0.3659458333333359</v>
       </c>
       <c r="F12" t="n">
-        <v>0.617186336687772</v>
+        <v>0.6166667176365763</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08202082933454902</v>
+        <v>0.08356590135120001</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>1.911676520349269</v>
+        <v>1.911673891242306</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -763,10 +763,10 @@
         <v>2.026650000000006</v>
       </c>
       <c r="F13" t="n">
-        <v>4.847005601046573</v>
+        <v>4.847525098359374</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6177454895451187</v>
+        <v>0.6176635458259863</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>1.904730701203715</v>
+        <v>1.903886307958609</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.183522283915429</v>
+        <v>2.182434499999999</v>
       </c>
       <c r="F14" t="n">
-        <v>4.268300854819174</v>
+        <v>4.267758114261001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02259642804652451</v>
+        <v>-0.02233638580071862</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5210135296924416</v>
+        <v>0.5218977650244685</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5879735494179048</v>
+        <v>0.5890613333333352</v>
       </c>
       <c r="F15" t="n">
-        <v>1.611122210876467</v>
+        <v>1.612509042886475</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8375896495675856</v>
+        <v>0.8373099280030788</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>6.493387576910424</v>
+        <v>6.494049892351112</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>4.951666666666667</v>
+        <v>4.951980666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>12.25065895364586</v>
+        <v>12.2506548938002</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6585808217042641</v>
+        <v>0.6585810479955918</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4908391624295461</v>
+        <v>0.490401844204891</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.566346558624384</v>
+        <v>0.5658026666666688</v>
       </c>
       <c r="F17" t="n">
-        <v>1.409197946123601</v>
+        <v>1.407409574735563</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8718487489406233</v>
+        <v>0.8721738084644485</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>5.502450866276585</v>
+        <v>5.502615626053483</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -893,10 +893,10 @@
         <v>4.223637500000001</v>
       </c>
       <c r="F18" t="n">
-        <v>12.28009363460324</v>
+        <v>12.28038579391981</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0216558886259437</v>
+        <v>-0.02170450223521425</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>6.436577540217171</v>
+        <v>6.434662625766387</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5.349543842539812</v>
+        <v>5.347912166666666</v>
       </c>
       <c r="F19" t="n">
-        <v>9.579497782353778</v>
+        <v>9.578833364758326</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8384882089536514</v>
+        <v>0.838510612540315</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>1.072534356843872</v>
+        <v>1.073890306903865</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.241710324126856</v>
+        <v>1.243342000000002</v>
       </c>
       <c r="F20" t="n">
-        <v>2.407973889417734</v>
+        <v>2.409558183538498</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8569549022280536</v>
+        <v>0.8567666110999755</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2052954076250633</v>
+        <v>0.204389397441972</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.235630617248761</v>
+        <v>0.2345818333333292</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3037467084284506</v>
+        <v>0.3030996192244383</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4072148267470654</v>
+        <v>-0.4012254708013667</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2074520790897316</v>
+        <v>0.2079305308900799</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2384701080422881</v>
+        <v>0.2390140000000033</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3071647865658278</v>
+        <v>0.3073597758176351</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.057308816064694</v>
+        <v>-2.061191628166005</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1928457935517812</v>
+        <v>0.1933253780722658</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2217242748253649</v>
+        <v>0.2222681667054699</v>
       </c>
       <c r="F23" t="n">
-        <v>0.279412539904949</v>
+        <v>0.279390359473839</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7572482424317706</v>
+        <v>-0.7569692644261803</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>0.4779971709702442</v>
+        <v>0.4788759105946081</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5822527162009857</v>
+        <v>0.5833404999805983</v>
       </c>
       <c r="F24" t="n">
-        <v>1.349718826528484</v>
+        <v>1.347986047077436</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8747219608841386</v>
+        <v>0.8750434202334482</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>2.41490816967546</v>
+        <v>2.414139078163236</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2.574305617287568</v>
+        <v>2.573331833333333</v>
       </c>
       <c r="F25" t="n">
-        <v>6.024546657190824</v>
+        <v>6.024479155487826</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7309206820937324</v>
+        <v>0.7309267118289072</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>2.84331338911722</v>
+        <v>2.844362088063133</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>3.073323549417903</v>
+        <v>3.074411333333334</v>
       </c>
       <c r="F26" t="n">
-        <v>6.993051393590013</v>
+        <v>6.993130970158549</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4998701692800471</v>
+        <v>0.49985878688345</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2694068102562513</v>
+        <v>0.2685369242391247</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3351181146876249</v>
+        <v>0.3340303289095494</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5530755508688879</v>
+        <v>0.5519198920813458</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.394975102939116</v>
+        <v>-5.368278251188426</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6384834633898508</v>
+        <v>0.6389366511397224</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7783242764939876</v>
+        <v>0.7788681682964823</v>
       </c>
       <c r="F28" t="n">
-        <v>1.86535078013801</v>
+        <v>1.865259226430935</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.7625105941994275</v>
+        <v>-0.7623375860763488</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>12.77530611600981</v>
+        <v>12.77593057048087</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>8.377341645867132</v>
+        <v>8.377341665677134</v>
       </c>
       <c r="F29" t="n">
-        <v>19.26551624713989</v>
+        <v>19.26546332062809</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6581653032733619</v>
+        <v>0.6581671814574734</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>0.2825328866275891</v>
+        <v>0.2829624628980459</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3651992747089483</v>
+        <v>0.3657431666666635</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4646035802540371</v>
+        <v>0.464059146130457</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3481209439044088</v>
+        <v>-0.3449632712664799</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>0.4820618069640865</v>
+        <v>0.4820150602218441</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.655933333333337</v>
+        <v>0.6559333333333358</v>
       </c>
       <c r="F31" t="n">
-        <v>1.464656636566821</v>
+        <v>1.462818797968726</v>
       </c>
       <c r="G31" t="n">
-        <v>0.891188762949484</v>
+        <v>0.8914616624418933</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1742844782591605</v>
+        <v>0.1742900164105319</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2421208333333323</v>
+        <v>0.2421208333333311</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2946531234383214</v>
+        <v>0.295241380072869</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1791544732855064</v>
+        <v>-0.1838673902500769</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>0.4158268064755641</v>
+        <v>0.4148379851802299</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5464855092064814</v>
+        <v>0.5450735000000032</v>
       </c>
       <c r="F33" t="n">
-        <v>1.761865501422216</v>
+        <v>1.763120641053053</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7931281532312193</v>
+        <v>0.7928333003714431</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1520865553019671</v>
+        <v>0.1517539925308126</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1981715586243809</v>
+        <v>0.1977333333333332</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2567069467099469</v>
+        <v>0.2558477544504424</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5531193643406787</v>
+        <v>0.5561057567339676</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1373033845874297</v>
+        <v>0.1368862091220599</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1779465586243809</v>
+        <v>0.1774026666666622</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2529759766541652</v>
+        <v>0.2536314197623456</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.292737060457368</v>
+        <v>-1.304633094986297</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2713606790374929</v>
+        <v>0.2722092747019991</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3513943827512414</v>
+        <v>0.3524821666666747</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4526923258033218</v>
+        <v>0.4532144267055095</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6682253092953035</v>
+        <v>0.6674595805883181</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1866843709136702</v>
+        <v>0.1866906663153083</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2421750000000079</v>
+        <v>0.2421750000000043</v>
       </c>
       <c r="F37" t="n">
-        <v>0.339072405647114</v>
+        <v>0.3382000483796617</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1425095605286122</v>
+        <v>0.1469161458900964</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1321712566528424</v>
+        <v>0.1321736859341112</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.171029166666667</v>
+        <v>0.1710291666666587</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1941620354483778</v>
+        <v>0.1945219558490256</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5616080639821204</v>
+        <v>0.559981253200738</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>1.058005064240611</v>
+        <v>1.058818088948546</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.169082608042287</v>
+        <v>1.170007166666672</v>
       </c>
       <c r="F39" t="n">
-        <v>4.360631130908504</v>
+        <v>4.361826458882492</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7524837865955821</v>
+        <v>0.7523480706426728</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1255996019870324</v>
+        <v>0.125387956396266</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.137577808624382</v>
+        <v>0.1373479166666662</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1661864256951152</v>
+        <v>0.166772466586964</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6799476366739344</v>
+        <v>0.6776863871800698</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1095735953399878</v>
+        <v>0.1085846280962656</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.120266033915429</v>
+        <v>0.1191782499999986</v>
       </c>
       <c r="F41" t="n">
-        <v>0.149038928337755</v>
+        <v>0.1484820250451219</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.3320435529053809</v>
+        <v>-0.3221074443126961</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1012231720224609</v>
+        <v>0.09974068280383575</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1112230092064775</v>
+        <v>0.1095913333333319</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1441118285939666</v>
+        <v>0.1436103439542801</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.1988570432715155</v>
+        <v>-0.1905279234929678</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>0.09784032223612699</v>
+        <v>0.09784410414481401</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1543,10 +1543,10 @@
         <v>0.1070791666666651</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1241474271155889</v>
+        <v>0.1249344172249292</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7914929211957067</v>
+        <v>0.788841023878221</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1417386162364037</v>
+        <v>0.1402869294962575</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1558980092064791</v>
+        <v>0.1542970000000009</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2073141455647193</v>
+        <v>0.205255895710697</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8719627419542264</v>
+        <v>0.8744924725575016</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2530781128577439</v>
+        <v>0.2535812931940201</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2776826080422848</v>
+        <v>0.2782265</v>
       </c>
       <c r="F45" t="n">
-        <v>0.327094824906457</v>
+        <v>0.3279850480189603</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7344678372659137</v>
+        <v>0.7330205227820012</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1631375496023836</v>
+        <v>0.1621526672177523</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1797764505820988</v>
+        <v>0.1786886666666684</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2506387457707461</v>
+        <v>0.2490191364614372</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6499500524453463</v>
+        <v>0.6544594300848057</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1220394171756531</v>
+        <v>0.1230303936013081</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1340027160845712</v>
+        <v>0.1350905000000016</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1726413357728526</v>
+        <v>0.174633523912221</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8516538011226119</v>
+        <v>0.8482103768046366</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>0.131876781711946</v>
+        <v>0.1313830133933797</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1445048919577143</v>
+        <v>0.1439609999999991</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1881297552921292</v>
+        <v>0.1872695983264037</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.4497744504613725</v>
+        <v>-0.4365475924379394</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1085721719961807</v>
+        <v>0.109071117770923</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1190034413756174</v>
+        <v>0.1195473333333326</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1420197359486613</v>
+        <v>0.1420716409327816</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.03049249215421801</v>
+        <v>-0.03124587294812553</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>0.08417586038812756</v>
+        <v>0.08284780944076883</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.09246884253981473</v>
+        <v>0.09100950000000314</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1225360392064436</v>
+        <v>0.1207430571116499</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1922996079553727</v>
+        <v>0.2157636789271203</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>0.4806914747747378</v>
+        <v>0.4798562360952343</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5566014505820966</v>
+        <v>0.5555136666666662</v>
       </c>
       <c r="F51" t="n">
-        <v>1.385237645025913</v>
+        <v>1.383159621973306</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9148302566165509</v>
+        <v>0.9150855946686332</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>0.7066606894311555</v>
+        <v>0.7074385587245842</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9290318827512394</v>
+        <v>0.9301196666666686</v>
       </c>
       <c r="F52" t="n">
-        <v>2.197615467886436</v>
+        <v>2.196413926689897</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7922393348994644</v>
+        <v>0.792466458123388</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3871224700073289</v>
+        <v>0.3878635191613216</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4945117747089505</v>
+        <v>0.4954363333333334</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9261011947811536</v>
+        <v>0.9273279730444135</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7658045941761071</v>
+        <v>0.7651837200696547</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>0.8611704522997843</v>
+        <v>0.8621149379518488</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0.97652844137562</v>
+        <v>0.9775946666666678</v>
       </c>
       <c r="F54" t="n">
-        <v>3.169840943536126</v>
+        <v>3.171194268177839</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8001370826795451</v>
+        <v>0.7999663882158643</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1071518878297224</v>
+        <v>0.1066604300808616</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.117804891957715</v>
+        <v>0.1172609999999998</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1449018970101873</v>
+        <v>0.1439833363876992</v>
       </c>
       <c r="G55" t="n">
-        <v>0.09957690772743832</v>
+        <v>0.1109566296329516</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1056094074610819</v>
+        <v>0.1050975813994897</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1161847839154326</v>
+        <v>0.1156193333333349</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1345560480284493</v>
+        <v>0.1340861626865365</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2165930793010858</v>
+        <v>0.2220550215957635</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>0.09475877828204558</v>
+        <v>0.09476155724393046</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1907,10 +1907,10 @@
         <v>0.1042458333333336</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1256072507777646</v>
+        <v>0.1254313505760559</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0147441741394394</v>
+        <v>0.01750174343919753</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1219438630120529</v>
+        <v>0.1219444414054229</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1933,10 +1933,10 @@
         <v>0.1336749999999967</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1565543693916878</v>
+        <v>0.1572858978336338</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6324741067993231</v>
+        <v>0.6290314206162975</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>0.06701327262550008</v>
+        <v>0.06506731619811192</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0.07354040116419291</v>
+        <v>0.07140383333333311</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0941297008175901</v>
+        <v>0.09261171834060485</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2109237913926373</v>
+        <v>0.2361686536690075</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>17.99657064895834</v>
+        <v>17.99944020546848</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>7.60957771608457</v>
+        <v>7.610665500000001</v>
       </c>
       <c r="F60" t="n">
-        <v>19.56198002345011</v>
+        <v>19.56198119969977</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3819017980538167</v>
+        <v>0.3819017237220957</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1884280613397027</v>
+        <v>0.1886597296743948</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.204954166666667</v>
+        <v>0.2052015</v>
       </c>
       <c r="F61" t="n">
-        <v>0.295522366696364</v>
+        <v>0.2956798772445172</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.9761821290341977</v>
+        <v>-0.9782892621469426</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1565561920054391</v>
+        <v>0.1560659165328387</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1717798919577174</v>
+        <v>0.1712360000000022</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1974877246724087</v>
+        <v>0.1961054628441906</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2434127778010458</v>
+        <v>0.2539667677877132</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>0.087162897655317</v>
+        <v>0.08765978857768435</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.09589927470895294</v>
+        <v>0.09644316666666815</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1173313345370585</v>
+        <v>0.1170129325074809</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.4671635647983621</v>
+        <v>-0.4592114860284213</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1204300892296484</v>
+        <v>0.1199385125588474</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1324090586243803</v>
+        <v>0.1318651666666651</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1730846530817285</v>
+        <v>0.1726174020987819</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.6227975597871842</v>
+        <v>-0.6140477339786508</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>0.4039839972711717</v>
+        <v>0.4039978833588181</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2115,10 +2115,10 @@
         <v>0.4454291666666658</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8196217473806605</v>
+        <v>0.8197908162496885</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.02020989883632529</v>
+        <v>-0.02063083330814175</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>3.166945511833908</v>
+        <v>3.165514895244392</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>3.107277175873148</v>
+        <v>3.105645500000003</v>
       </c>
       <c r="F66" t="n">
-        <v>6.408706892697335</v>
+        <v>6.408676714176832</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.3946244935956862</v>
+        <v>-0.3946113590880598</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>5.105888462194914</v>
+        <v>5.106380730743454</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>4.175103441375622</v>
+        <v>4.175647333333337</v>
       </c>
       <c r="F67" t="n">
-        <v>10.03255547797156</v>
+        <v>10.03255964453027</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7716271908835236</v>
+        <v>0.7716270011952796</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1035391884844993</v>
+        <v>0.1040203700224833</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1131999999999997</v>
+        <v>0.1137223333333323</v>
       </c>
       <c r="F68" t="n">
-        <v>0.142564831154608</v>
+        <v>0.1427373797947362</v>
       </c>
       <c r="G68" t="n">
-        <v>0.478576001592266</v>
+        <v>0.4773130611062659</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>0.08859480667405106</v>
+        <v>0.09009081852200898</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.09677282412685351</v>
+        <v>0.09840449999999912</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1253752227240565</v>
+        <v>0.126016084518341</v>
       </c>
       <c r="G69" t="n">
-        <v>0.6573559160425884</v>
+        <v>0.6538440783129783</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>0.1036616077910084</v>
+        <v>0.1051626433115525</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1131103241268517</v>
+        <v>0.1147419999999973</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1446148749765505</v>
+        <v>0.1443820934730676</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4308913362885087</v>
+        <v>0.4327220103160445</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>0.09661895513843831</v>
+        <v>0.09612227357529297</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1051257252910514</v>
+        <v>0.1045818333333361</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1231882138957663</v>
+        <v>0.122908444003388</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.5915104615724784</v>
+        <v>-0.5842897853340747</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>0.09413425489744874</v>
+        <v>0.09342717779660101</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1025722839154331</v>
+        <v>0.1017985000000022</v>
       </c>
       <c r="F72" t="n">
-        <v>0.131391897035927</v>
+        <v>0.1304709745460667</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1138107365016436</v>
+        <v>0.1261897581687533</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>1.597832729903202</v>
+        <v>1.596737294961551</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.872735509206479</v>
+        <v>1.871484499999998</v>
       </c>
       <c r="F73" t="n">
-        <v>4.963941392957306</v>
+        <v>4.962600893150586</v>
       </c>
       <c r="G73" t="n">
-        <v>0.771575935612692</v>
+        <v>0.7716992896353654</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>0.4938534505782488</v>
+        <v>0.4935412230594872</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6333923919577137</v>
+        <v>0.6330291666666668</v>
       </c>
       <c r="F74" t="n">
-        <v>1.395625526887047</v>
+        <v>1.397101367417797</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8874501303937631</v>
+        <v>0.8872119669574119</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>3.433641256268275</v>
+        <v>3.435072830056776</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>3.61754782412686</v>
+        <v>3.619179500000004</v>
       </c>
       <c r="F75" t="n">
-        <v>8.997053913133053</v>
+        <v>8.996952993966385</v>
       </c>
       <c r="G75" t="n">
-        <v>0.498773214723321</v>
+        <v>0.4987844590942618</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>0.4162268660766181</v>
+        <v>0.4162674629751451</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5312416666666581</v>
+        <v>0.5312806666666544</v>
       </c>
       <c r="F76" t="n">
-        <v>1.029366397419929</v>
+        <v>1.029384127317879</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.035564493241471</v>
+        <v>-1.035634615331404</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>1.304893233255421</v>
+        <v>1.304916236365168</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1.664908333333337</v>
+        <v>1.664908333333339</v>
       </c>
       <c r="F77" t="n">
-        <v>3.525966783773669</v>
+        <v>3.525196429022174</v>
       </c>
       <c r="G77" t="n">
-        <v>0.6312267054913343</v>
+        <v>0.6313878273869302</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>1.382878714464392</v>
+        <v>1.383675101057886</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1.919611049417902</v>
+        <v>1.920698833333329</v>
       </c>
       <c r="F78" t="n">
-        <v>2.935723967719249</v>
+        <v>2.93561301045295</v>
       </c>
       <c r="G78" t="n">
-        <v>0.7166203653490224</v>
+        <v>0.7166417859156209</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>1.070741508980986</v>
+        <v>1.071152331534258</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>1.366824274708948</v>
+        <v>1.367368166666663</v>
       </c>
       <c r="F79" t="n">
-        <v>2.807801566546829</v>
+        <v>2.808561243455566</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7338356936120005</v>
+        <v>0.7336916476556918</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>0.6302177738636836</v>
+        <v>0.6298183355935717</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8101840586243819</v>
+        <v>0.8096401666666685</v>
       </c>
       <c r="F80" t="n">
-        <v>1.93401964798922</v>
+        <v>1.934051919752674</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.100459896438425</v>
+        <v>-1.100529995116626</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1569214020130271</v>
+        <v>0.1569254505922636</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2047666666666667</v>
+        <v>0.2047666666666643</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2534794838107563</v>
+        <v>0.2538374687157114</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2415609188101969</v>
+        <v>0.2394171439951271</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>3.394825712728047</v>
+        <v>3.394658577890263</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3.48458405862438</v>
+        <v>3.484487500000002</v>
       </c>
       <c r="F82" t="n">
-        <v>7.052692978633079</v>
+        <v>7.05349211884728</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7556143186879032</v>
+        <v>0.7555589328967083</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>2.067110719356967</v>
+        <v>2.067363767980537</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>2.438141682760545</v>
+        <v>2.438324695652173</v>
       </c>
       <c r="F83" t="n">
-        <v>4.839087274774348</v>
+        <v>4.837889527749777</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7752556906568751</v>
+        <v>0.7753669320950322</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/testing_daily_metrics/agus2_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus2_testing_daily_metrics.xlsx
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1933253780722658</v>
+        <v>0.1933253780383106</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2222681667054699</v>
+        <v>0.2222681666666647</v>
       </c>
       <c r="F23" t="n">
-        <v>0.279390359473839</v>
+        <v>0.2793903594865054</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7569692644261803</v>
+        <v>-0.7569692645854877</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>0.4788759105946081</v>
+        <v>0.4788759106118591</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5833404999805983</v>
+        <v>0.5833405000000008</v>
       </c>
       <c r="F24" t="n">
-        <v>1.347986047077436</v>
+        <v>1.347986047259883</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8750434202334482</v>
+        <v>0.875043420199623</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2685369242391247</v>
+        <v>0.2685369277880248</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3340303289095494</v>
+        <v>0.3340303333333316</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5519198920813458</v>
+        <v>0.5519198925786247</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.368278251188426</v>
+        <v>-5.368278262664043</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6389366511397224</v>
+        <v>0.6389366497772273</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7788681682964823</v>
+        <v>0.7788681666860704</v>
       </c>
       <c r="F28" t="n">
-        <v>1.865259226430935</v>
+        <v>1.865259221950704</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.7623375860763488</v>
+        <v>-0.7623375776103107</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>12.77593057048087</v>
+        <v>12.77593057101986</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>8.377341665677134</v>
+        <v>8.377341666356223</v>
       </c>
       <c r="F29" t="n">
-        <v>19.26546332062809</v>
+        <v>19.26546332065917</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6581671814574734</v>
+        <v>0.6581671814563703</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
